--- a/WDL/WDL.xlsx
+++ b/WDL/WDL.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$100</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="200">
   <si>
     <t>Duy Dương</t>
   </si>
@@ -620,6 +620,9 @@
   </si>
   <si>
     <t>BLACK LIST</t>
+  </si>
+  <si>
+    <t>Bình - bạn Thành</t>
   </si>
 </sst>
 </file>
@@ -656,7 +659,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -678,6 +681,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,7 +768,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -771,6 +780,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1056,7 +1066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1094,13 +1104,13 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5">
-        <v>1000</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="11">
+        <v>1000</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>93</v>
       </c>
       <c r="E2" s="3" t="s">
@@ -1117,13 +1127,13 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="11">
         <v>200</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="11" t="s">
         <v>178</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -1140,13 +1150,13 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5">
-        <v>500</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="11">
+        <v>500</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -1163,13 +1173,13 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5">
-        <v>500</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="11">
+        <v>500</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -1209,13 +1219,13 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="5">
-        <v>500</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="11">
+        <v>500</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -1315,13 +1325,13 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="4">
-        <v>300</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="B12" s="11">
+        <v>300</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1355,13 +1365,13 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="4">
-        <v>300</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="11">
+        <v>300</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -1375,13 +1385,13 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="4">
-        <v>500</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="B15" s="11">
+        <v>500</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1415,13 +1425,13 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="11">
         <v>200</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="11" t="s">
         <v>93</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1655,13 +1665,13 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="4">
-        <v>1000</v>
-      </c>
-      <c r="C29" s="4" t="s">
+      <c r="B29" s="11">
+        <v>1000</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -1755,13 +1765,13 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="4">
-        <v>500</v>
-      </c>
-      <c r="C34" s="4" t="s">
+      <c r="B34" s="11">
+        <v>500</v>
+      </c>
+      <c r="C34" s="11" t="s">
         <v>93</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -1856,7 +1866,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>37</v>
+        <v>199</v>
       </c>
       <c r="B39" s="4">
         <v>200</v>
@@ -2169,13 +2179,13 @@
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B55" s="4">
-        <v>500</v>
-      </c>
-      <c r="C55" s="4" t="s">
+      <c r="B55" s="11">
+        <v>500</v>
+      </c>
+      <c r="C55" s="11" t="s">
         <v>93</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -2409,13 +2419,13 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="B67" s="4">
-        <v>500</v>
-      </c>
-      <c r="C67" s="4" t="s">
+      <c r="B67" s="11">
+        <v>500</v>
+      </c>
+      <c r="C67" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -2627,13 +2637,13 @@
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B78" s="4">
-        <v>1000</v>
-      </c>
-      <c r="C78" s="4" t="s">
+      <c r="B78" s="11">
+        <v>1000</v>
+      </c>
+      <c r="C78" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E78" s="1" t="s">
@@ -2688,13 +2698,13 @@
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B81" s="4">
-        <v>1000</v>
-      </c>
-      <c r="C81" s="4" t="s">
+      <c r="B81" s="11">
+        <v>1000</v>
+      </c>
+      <c r="C81" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E81" s="1" t="s">
@@ -2748,13 +2758,13 @@
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B84" s="4">
-        <v>500</v>
-      </c>
-      <c r="C84" s="4" t="s">
+      <c r="B84" s="11">
+        <v>500</v>
+      </c>
+      <c r="C84" s="11" t="s">
         <v>186</v>
       </c>
       <c r="E84" s="1" t="s">
@@ -2768,13 +2778,13 @@
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B85" s="4">
-        <v>300</v>
-      </c>
-      <c r="C85" s="4" t="s">
+      <c r="B85" s="11">
+        <v>300</v>
+      </c>
+      <c r="C85" s="11" t="s">
         <v>93</v>
       </c>
       <c r="E85" s="1" t="s">
@@ -2828,13 +2838,13 @@
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B88" s="4">
-        <v>500</v>
-      </c>
-      <c r="C88" s="4" t="s">
+      <c r="B88" s="11">
+        <v>500</v>
+      </c>
+      <c r="C88" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E88" s="1" t="s">
@@ -2908,13 +2918,13 @@
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B92" s="4">
-        <v>500</v>
-      </c>
-      <c r="C92" s="4" t="s">
+      <c r="B92" s="11">
+        <v>500</v>
+      </c>
+      <c r="C92" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E92" s="1" t="s">
@@ -2948,13 +2958,13 @@
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B94" s="4">
-        <v>1000</v>
-      </c>
-      <c r="C94" s="4" t="s">
+      <c r="B94" s="11">
+        <v>1000</v>
+      </c>
+      <c r="C94" s="11" t="s">
         <v>176</v>
       </c>
       <c r="E94" s="1" t="s">
@@ -3060,61 +3070,50 @@
         <v>180</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B101" s="4">
-        <v>200</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A103" s="8"/>
-      <c r="B103" s="9" t="s">
+    <row r="102" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A102" s="8"/>
+      <c r="B102" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="C103" s="10"/>
+      <c r="C102" s="10"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B103" s="7"/>
+      <c r="C103" s="7"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B104" s="7"/>
-      <c r="C104" s="7"/>
+      <c r="A104" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B108" s="6"/>
-      <c r="C108" s="6"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C101"/>
+  <autoFilter ref="A1:C100"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
